--- a/artfynd/A 54537-2025 artfynd.xlsx
+++ b/artfynd/A 54537-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129977109</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129977207</v>
       </c>
       <c r="B4" t="n">
-        <v>96283</v>
+        <v>96286</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54537-2025 artfynd.xlsx
+++ b/artfynd/A 54537-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129977109</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129977207</v>
       </c>
       <c r="B4" t="n">
-        <v>96286</v>
+        <v>96287</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54537-2025 artfynd.xlsx
+++ b/artfynd/A 54537-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129977109</v>
       </c>
       <c r="B3" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129977207</v>
       </c>
       <c r="B4" t="n">
-        <v>96287</v>
+        <v>96304</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54537-2025 artfynd.xlsx
+++ b/artfynd/A 54537-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>129977207</v>
       </c>
       <c r="B4" t="n">
-        <v>96320</v>
+        <v>96322</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54537-2025 artfynd.xlsx
+++ b/artfynd/A 54537-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129977109</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129977207</v>
       </c>
       <c r="B4" t="n">
-        <v>96322</v>
+        <v>96409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54537-2025 artfynd.xlsx
+++ b/artfynd/A 54537-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129977051</v>
+        <v>129977207</v>
       </c>
       <c r="B2" t="n">
-        <v>5197</v>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,32 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>654783</v>
+        <v>654792</v>
       </c>
       <c r="R2" t="n">
-        <v>6684278</v>
+        <v>6684267</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +759,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hittad av Basti.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,11 +794,11 @@
         <v>129977109</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129977207</v>
+        <v>129977051</v>
       </c>
       <c r="B4" t="n">
-        <v>96409</v>
+        <v>5199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,27 +912,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -940,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654792</v>
+        <v>654783</v>
       </c>
       <c r="R4" t="n">
-        <v>6684267</v>
+        <v>6684278</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -975,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -985,12 +990,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hittad av Basti.</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 54537-2025 artfynd.xlsx
+++ b/artfynd/A 54537-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129977207</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129977109</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,8 +1029,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129977051</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>